--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167934</v>
+        <v>125167916</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881252</v>
+        <v>881689</v>
       </c>
       <c r="R3" t="n">
-        <v>7392697</v>
+        <v>7392822</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167935</v>
+        <v>125167913</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881257</v>
+        <v>881154</v>
       </c>
       <c r="R4" t="n">
-        <v>7392746</v>
+        <v>7392722</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -963,6 +971,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167913</v>
+        <v>125167938</v>
       </c>
       <c r="B5" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,41 +1002,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881154</v>
+        <v>881678</v>
       </c>
       <c r="R5" t="n">
-        <v>7392722</v>
+        <v>7392828</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1062,13 +1068,17 @@
           <t>2025-05-17</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1087,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167937</v>
+        <v>125167940</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1109,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881533</v>
+        <v>881680</v>
       </c>
       <c r="R6" t="n">
-        <v>7392766</v>
+        <v>7392834</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1163,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167940</v>
+        <v>125167937</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1216,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881680</v>
+        <v>881533</v>
       </c>
       <c r="R7" t="n">
-        <v>7392834</v>
+        <v>7392766</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1265,11 +1280,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167938</v>
+        <v>125167939</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,25 +1318,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1336,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881678</v>
+        <v>881160</v>
       </c>
       <c r="R8" t="n">
-        <v>7392828</v>
+        <v>7392721</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1376,7 +1386,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167926</v>
+        <v>125167935</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1527,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1555,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881656</v>
+        <v>881257</v>
       </c>
       <c r="R10" t="n">
-        <v>7392806</v>
+        <v>7392746</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,11 +1591,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167929</v>
+        <v>125167926</v>
       </c>
       <c r="B12" t="n">
-        <v>79919</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,25 +1731,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881423</v>
+        <v>881656</v>
       </c>
       <c r="R12" t="n">
-        <v>7392740</v>
+        <v>7392806</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1790,6 +1795,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1816,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167939</v>
+        <v>125167934</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881160</v>
+        <v>881252</v>
       </c>
       <c r="R13" t="n">
-        <v>7392721</v>
+        <v>7392697</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1892,11 +1902,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167916</v>
+        <v>125167929</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>79919</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881689</v>
+        <v>881423</v>
       </c>
       <c r="R14" t="n">
-        <v>7392822</v>
+        <v>7392740</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1719,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167926</v>
+        <v>125167934</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,25 +1731,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881656</v>
+        <v>881252</v>
       </c>
       <c r="R12" t="n">
-        <v>7392806</v>
+        <v>7392697</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1795,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167934</v>
+        <v>125167926</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881252</v>
+        <v>881656</v>
       </c>
       <c r="R13" t="n">
-        <v>7392697</v>
+        <v>7392806</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1902,6 +1897,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167928</v>
+        <v>125167913</v>
       </c>
       <c r="B2" t="n">
-        <v>79795</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881195</v>
+        <v>881154</v>
       </c>
       <c r="R2" t="n">
-        <v>7392757</v>
+        <v>7392722</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -759,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167916</v>
+        <v>125167928</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881689</v>
+        <v>881195</v>
       </c>
       <c r="R3" t="n">
-        <v>7392822</v>
+        <v>7392757</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167913</v>
+        <v>125167939</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>56714</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +895,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881154</v>
+        <v>881160</v>
       </c>
       <c r="R4" t="n">
-        <v>7392722</v>
+        <v>7392721</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -965,13 +961,17 @@
           <t>2025-05-17</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167938</v>
+        <v>125167927</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881678</v>
+        <v>881360</v>
       </c>
       <c r="R5" t="n">
-        <v>7392828</v>
+        <v>7392796</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1066,11 +1066,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167940</v>
+        <v>125167916</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,16 +1108,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1137,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881680</v>
+        <v>881689</v>
       </c>
       <c r="R6" t="n">
-        <v>7392834</v>
+        <v>7392822</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1177,7 +1172,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167937</v>
+        <v>125167933</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881533</v>
+        <v>881273</v>
       </c>
       <c r="R7" t="n">
-        <v>7392766</v>
+        <v>7392683</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1306,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167939</v>
+        <v>125167937</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881160</v>
+        <v>881533</v>
       </c>
       <c r="R8" t="n">
-        <v>7392721</v>
+        <v>7392766</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1382,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167933</v>
+        <v>125167934</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1453,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881273</v>
+        <v>881252</v>
       </c>
       <c r="R9" t="n">
-        <v>7392683</v>
+        <v>7392697</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1515,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167935</v>
+        <v>125167940</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1555,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881257</v>
+        <v>881680</v>
       </c>
       <c r="R10" t="n">
-        <v>7392746</v>
+        <v>7392834</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1591,6 +1581,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167927</v>
+        <v>125167929</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>79919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1633,21 +1628,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1657,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881360</v>
+        <v>881423</v>
       </c>
       <c r="R11" t="n">
-        <v>7392796</v>
+        <v>7392740</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1719,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167934</v>
+        <v>125167935</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881252</v>
+        <v>881257</v>
       </c>
       <c r="R12" t="n">
-        <v>7392697</v>
+        <v>7392746</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1821,10 +1816,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167926</v>
+        <v>125167938</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1828,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881656</v>
+        <v>881678</v>
       </c>
       <c r="R13" t="n">
-        <v>7392806</v>
+        <v>7392828</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1901,7 +1896,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Hack på gran</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167929</v>
+        <v>125167926</v>
       </c>
       <c r="B14" t="n">
-        <v>79919</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881423</v>
+        <v>881656</v>
       </c>
       <c r="R14" t="n">
-        <v>7392740</v>
+        <v>7392806</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,6 +1999,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167913</v>
+        <v>125167916</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881154</v>
+        <v>881689</v>
       </c>
       <c r="R2" t="n">
-        <v>7392722</v>
+        <v>7392822</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -756,13 +753,17 @@
           <t>2025-05-17</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Avbarkade granar</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167928</v>
+        <v>125167927</v>
       </c>
       <c r="B3" t="n">
         <v>79795</v>
@@ -821,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881195</v>
+        <v>881360</v>
       </c>
       <c r="R3" t="n">
-        <v>7392757</v>
+        <v>7392796</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -883,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167939</v>
+        <v>125167940</v>
       </c>
       <c r="B4" t="n">
         <v>56714</v>
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881160</v>
+        <v>881680</v>
       </c>
       <c r="R4" t="n">
-        <v>7392721</v>
+        <v>7392834</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -990,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167927</v>
+        <v>125167929</v>
       </c>
       <c r="B5" t="n">
-        <v>79795</v>
+        <v>79919</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881360</v>
+        <v>881423</v>
       </c>
       <c r="R5" t="n">
-        <v>7392796</v>
+        <v>7392740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167916</v>
+        <v>125167926</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1108,16 +1109,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1132,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881689</v>
+        <v>881656</v>
       </c>
       <c r="R6" t="n">
-        <v>7392822</v>
+        <v>7392806</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1172,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Avbarkade granar</t>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167933</v>
+        <v>125167934</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1239,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881273</v>
+        <v>881252</v>
       </c>
       <c r="R7" t="n">
-        <v>7392683</v>
+        <v>7392697</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1301,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167937</v>
+        <v>125167938</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1341,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881533</v>
+        <v>881678</v>
       </c>
       <c r="R8" t="n">
-        <v>7392766</v>
+        <v>7392828</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1377,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,7 +1409,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167934</v>
+        <v>125167935</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1443,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881252</v>
+        <v>881257</v>
       </c>
       <c r="R9" t="n">
-        <v>7392697</v>
+        <v>7392746</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1505,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167940</v>
+        <v>125167933</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881680</v>
+        <v>881273</v>
       </c>
       <c r="R10" t="n">
-        <v>7392834</v>
+        <v>7392683</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167929</v>
+        <v>125167928</v>
       </c>
       <c r="B11" t="n">
-        <v>79919</v>
+        <v>79795</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881423</v>
+        <v>881195</v>
       </c>
       <c r="R11" t="n">
-        <v>7392740</v>
+        <v>7392757</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1714,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167935</v>
+        <v>125167913</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,38 +1727,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881257</v>
+        <v>881154</v>
       </c>
       <c r="R12" t="n">
-        <v>7392746</v>
+        <v>7392722</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1798,6 +1802,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1816,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167938</v>
+        <v>125167939</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881678</v>
+        <v>881160</v>
       </c>
       <c r="R13" t="n">
-        <v>7392828</v>
+        <v>7392721</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1896,7 +1901,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167926</v>
+        <v>125167937</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1940,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881656</v>
+        <v>881533</v>
       </c>
       <c r="R14" t="n">
-        <v>7392806</v>
+        <v>7392766</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167916</v>
+        <v>125167940</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881689</v>
+        <v>881680</v>
       </c>
       <c r="R2" t="n">
-        <v>7392822</v>
+        <v>7392834</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkade granar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167927</v>
+        <v>125167938</v>
       </c>
       <c r="B3" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881360</v>
+        <v>881678</v>
       </c>
       <c r="R3" t="n">
-        <v>7392796</v>
+        <v>7392828</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -858,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167940</v>
+        <v>125167929</v>
       </c>
       <c r="B4" t="n">
-        <v>56714</v>
+        <v>79919</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6461</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881680</v>
+        <v>881423</v>
       </c>
       <c r="R4" t="n">
-        <v>7392834</v>
+        <v>7392740</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -960,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167929</v>
+        <v>125167935</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881423</v>
+        <v>881257</v>
       </c>
       <c r="R5" t="n">
-        <v>7392740</v>
+        <v>7392746</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167926</v>
+        <v>125167927</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>79795</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881656</v>
+        <v>881360</v>
       </c>
       <c r="R6" t="n">
-        <v>7392806</v>
+        <v>7392796</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1169,11 +1169,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167934</v>
+        <v>125167933</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1240,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881252</v>
+        <v>881273</v>
       </c>
       <c r="R7" t="n">
-        <v>7392697</v>
+        <v>7392683</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1302,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167938</v>
+        <v>125167916</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1314,25 +1309,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881678</v>
+        <v>881689</v>
       </c>
       <c r="R8" t="n">
-        <v>7392828</v>
+        <v>7392822</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1382,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167935</v>
+        <v>125167928</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1421,25 +1416,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881257</v>
+        <v>881195</v>
       </c>
       <c r="R9" t="n">
-        <v>7392746</v>
+        <v>7392757</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1511,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167933</v>
+        <v>125167913</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,38 +1518,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881273</v>
+        <v>881154</v>
       </c>
       <c r="R10" t="n">
-        <v>7392683</v>
+        <v>7392722</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1595,6 +1593,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1613,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167928</v>
+        <v>125167937</v>
       </c>
       <c r="B11" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881195</v>
+        <v>881533</v>
       </c>
       <c r="R11" t="n">
-        <v>7392757</v>
+        <v>7392766</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1715,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167913</v>
+        <v>125167926</v>
       </c>
       <c r="B12" t="n">
-        <v>90977</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,41 +1726,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881154</v>
+        <v>881656</v>
       </c>
       <c r="R12" t="n">
-        <v>7392722</v>
+        <v>7392806</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1796,13 +1792,17 @@
           <t>2025-05-17</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167939</v>
+        <v>125167934</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881160</v>
+        <v>881252</v>
       </c>
       <c r="R13" t="n">
-        <v>7392721</v>
+        <v>7392697</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1897,11 +1897,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167937</v>
+        <v>125167939</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881533</v>
+        <v>881160</v>
       </c>
       <c r="R14" t="n">
-        <v>7392766</v>
+        <v>7392721</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,6 +1999,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167940</v>
+        <v>125167913</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>90977</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881680</v>
+        <v>881154</v>
       </c>
       <c r="R2" t="n">
-        <v>7392834</v>
+        <v>7392722</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,17 +756,13 @@
           <t>2025-05-17</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spillning</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167938</v>
+        <v>125167940</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881678</v>
+        <v>881680</v>
       </c>
       <c r="R3" t="n">
-        <v>7392828</v>
+        <v>7392834</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167929</v>
+        <v>125167916</v>
       </c>
       <c r="B4" t="n">
-        <v>79919</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +900,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881423</v>
+        <v>881689</v>
       </c>
       <c r="R4" t="n">
-        <v>7392740</v>
+        <v>7392822</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -965,6 +964,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167935</v>
+        <v>125167929</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79919</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1007,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881257</v>
+        <v>881423</v>
       </c>
       <c r="R5" t="n">
-        <v>7392746</v>
+        <v>7392740</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1093,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167927</v>
+        <v>125167937</v>
       </c>
       <c r="B6" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1109,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881360</v>
+        <v>881533</v>
       </c>
       <c r="R6" t="n">
-        <v>7392796</v>
+        <v>7392766</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1297,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167916</v>
+        <v>125167927</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>79795</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1309,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881689</v>
+        <v>881360</v>
       </c>
       <c r="R8" t="n">
-        <v>7392822</v>
+        <v>7392796</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1373,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167928</v>
+        <v>125167938</v>
       </c>
       <c r="B9" t="n">
-        <v>79795</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881195</v>
+        <v>881678</v>
       </c>
       <c r="R9" t="n">
-        <v>7392757</v>
+        <v>7392828</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1480,6 +1479,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167913</v>
+        <v>125167928</v>
       </c>
       <c r="B10" t="n">
-        <v>90977</v>
+        <v>79795</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,37 +1526,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881154</v>
+        <v>881195</v>
       </c>
       <c r="R10" t="n">
-        <v>7392722</v>
+        <v>7392757</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1593,7 +1594,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1612,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167937</v>
+        <v>125167935</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881533</v>
+        <v>881257</v>
       </c>
       <c r="R11" t="n">
-        <v>7392766</v>
+        <v>7392746</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1714,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167926</v>
+        <v>125167939</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,16 +1730,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881656</v>
+        <v>881160</v>
       </c>
       <c r="R12" t="n">
-        <v>7392806</v>
+        <v>7392721</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Hack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167939</v>
+        <v>125167926</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,16 +1939,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881160</v>
+        <v>881656</v>
       </c>
       <c r="R14" t="n">
-        <v>7392721</v>
+        <v>7392806</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167940</v>
+        <v>125167935</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881680</v>
+        <v>881257</v>
       </c>
       <c r="R3" t="n">
-        <v>7392834</v>
+        <v>7392746</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -857,11 +857,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167916</v>
+        <v>125167937</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,25 +895,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881689</v>
+        <v>881533</v>
       </c>
       <c r="R4" t="n">
-        <v>7392822</v>
+        <v>7392766</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -964,11 +959,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,10 +985,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167929</v>
+        <v>125167933</v>
       </c>
       <c r="B5" t="n">
-        <v>79919</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,25 +997,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881423</v>
+        <v>881273</v>
       </c>
       <c r="R5" t="n">
-        <v>7392740</v>
+        <v>7392683</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1097,7 +1087,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167937</v>
+        <v>125167934</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1137,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881533</v>
+        <v>881252</v>
       </c>
       <c r="R6" t="n">
-        <v>7392766</v>
+        <v>7392697</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1199,10 +1189,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167933</v>
+        <v>125167928</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1201,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881273</v>
+        <v>881195</v>
       </c>
       <c r="R7" t="n">
-        <v>7392683</v>
+        <v>7392757</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1301,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167927</v>
+        <v>125167916</v>
       </c>
       <c r="B8" t="n">
-        <v>79795</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,25 +1303,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1331,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881360</v>
+        <v>881689</v>
       </c>
       <c r="R8" t="n">
-        <v>7392796</v>
+        <v>7392822</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1377,6 +1367,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1403,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167938</v>
+        <v>125167939</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881678</v>
+        <v>881160</v>
       </c>
       <c r="R9" t="n">
-        <v>7392828</v>
+        <v>7392721</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1483,7 +1478,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 kvm</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167928</v>
+        <v>125167926</v>
       </c>
       <c r="B10" t="n">
-        <v>79795</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881195</v>
+        <v>881656</v>
       </c>
       <c r="R10" t="n">
-        <v>7392757</v>
+        <v>7392806</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1586,6 +1581,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167935</v>
+        <v>125167929</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79919</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881257</v>
+        <v>881423</v>
       </c>
       <c r="R11" t="n">
-        <v>7392746</v>
+        <v>7392740</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1714,7 +1714,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167939</v>
+        <v>125167940</v>
       </c>
       <c r="B12" t="n">
         <v>56714</v>
@@ -1754,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881160</v>
+        <v>881680</v>
       </c>
       <c r="R12" t="n">
-        <v>7392721</v>
+        <v>7392834</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167934</v>
+        <v>125167927</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>79795</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881252</v>
+        <v>881360</v>
       </c>
       <c r="R13" t="n">
-        <v>7392697</v>
+        <v>7392796</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1923,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167926</v>
+        <v>125167938</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1963,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881656</v>
+        <v>881678</v>
       </c>
       <c r="R14" t="n">
-        <v>7392806</v>
+        <v>7392828</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2003,7 +2003,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack på gran</t>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167913</v>
+        <v>125167935</v>
       </c>
       <c r="B2" t="n">
-        <v>90977</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881154</v>
+        <v>881257</v>
       </c>
       <c r="R2" t="n">
-        <v>7392722</v>
+        <v>7392746</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -762,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167935</v>
+        <v>125167913</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>91131</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881257</v>
+        <v>881154</v>
       </c>
       <c r="R3" t="n">
-        <v>7392746</v>
+        <v>7392722</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,6 +864,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167937</v>
+        <v>125167938</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881533</v>
+        <v>881678</v>
       </c>
       <c r="R4" t="n">
-        <v>7392766</v>
+        <v>7392828</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167933</v>
+        <v>125167928</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>79932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1025,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881273</v>
+        <v>881195</v>
       </c>
       <c r="R5" t="n">
-        <v>7392683</v>
+        <v>7392757</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1087,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167934</v>
+        <v>125167926</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,25 +1104,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1132,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881252</v>
+        <v>881656</v>
       </c>
       <c r="R6" t="n">
-        <v>7392697</v>
+        <v>7392806</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1163,6 +1168,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167928</v>
+        <v>125167933</v>
       </c>
       <c r="B7" t="n">
-        <v>79795</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1229,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881195</v>
+        <v>881273</v>
       </c>
       <c r="R7" t="n">
-        <v>7392757</v>
+        <v>7392683</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1291,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167916</v>
+        <v>125167929</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>80056</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,25 +1313,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1331,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881689</v>
+        <v>881423</v>
       </c>
       <c r="R8" t="n">
-        <v>7392822</v>
+        <v>7392740</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1367,11 +1377,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1398,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167939</v>
+        <v>125167916</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,16 +1419,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1438,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881160</v>
+        <v>881689</v>
       </c>
       <c r="R9" t="n">
-        <v>7392721</v>
+        <v>7392822</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1478,7 +1483,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,10 +1510,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167926</v>
+        <v>125167927</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>79932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,25 +1522,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881656</v>
+        <v>881360</v>
       </c>
       <c r="R10" t="n">
-        <v>7392806</v>
+        <v>7392796</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,11 +1586,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167929</v>
+        <v>125167940</v>
       </c>
       <c r="B11" t="n">
-        <v>79919</v>
+        <v>56828</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6461</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881423</v>
+        <v>881680</v>
       </c>
       <c r="R11" t="n">
-        <v>7392740</v>
+        <v>7392834</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1688,6 +1688,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,10 +1719,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167940</v>
+        <v>125167939</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>56828</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1754,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881680</v>
+        <v>881160</v>
       </c>
       <c r="R12" t="n">
-        <v>7392834</v>
+        <v>7392721</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1821,10 +1826,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167927</v>
+        <v>125167934</v>
       </c>
       <c r="B13" t="n">
-        <v>79795</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,25 +1838,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1866,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881360</v>
+        <v>881252</v>
       </c>
       <c r="R13" t="n">
-        <v>7392796</v>
+        <v>7392697</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1923,10 +1928,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167938</v>
+        <v>125167937</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1963,10 +1968,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881678</v>
+        <v>881533</v>
       </c>
       <c r="R14" t="n">
-        <v>7392828</v>
+        <v>7392766</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1999,11 +2004,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -990,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167928</v>
+        <v>125167933</v>
       </c>
       <c r="B5" t="n">
-        <v>79932</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881195</v>
+        <v>881273</v>
       </c>
       <c r="R5" t="n">
-        <v>7392757</v>
+        <v>7392683</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167933</v>
+        <v>125167928</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>79932</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881273</v>
+        <v>881195</v>
       </c>
       <c r="R7" t="n">
-        <v>7392683</v>
+        <v>7392757</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -2028,6 +2028,618 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125616392</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>881164</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7392734</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125616388</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92646</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>881292</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7392783</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125616394</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>881602</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7392791</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>125616395</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>881585</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7392791</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125616387</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79932</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>881498</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7392797</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>125616393</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98269</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Hiirivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>881422</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7392746</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167913</v>
+        <v>125167938</v>
       </c>
       <c r="B3" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881154</v>
+        <v>881678</v>
       </c>
       <c r="R3" t="n">
-        <v>7392722</v>
+        <v>7392828</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -858,13 +855,17 @@
           <t>2025-05-17</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -883,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125167938</v>
+        <v>125167933</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -923,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>881678</v>
+        <v>881273</v>
       </c>
       <c r="R4" t="n">
-        <v>7392828</v>
+        <v>7392683</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -959,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167933</v>
+        <v>125167928</v>
       </c>
       <c r="B5" t="n">
-        <v>98269</v>
+        <v>79932</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1030,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881273</v>
+        <v>881195</v>
       </c>
       <c r="R5" t="n">
-        <v>7392683</v>
+        <v>7392757</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1092,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167926</v>
+        <v>125167934</v>
       </c>
       <c r="B6" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1132,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881656</v>
+        <v>881252</v>
       </c>
       <c r="R6" t="n">
-        <v>7392806</v>
+        <v>7392697</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1168,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167928</v>
+        <v>125167937</v>
       </c>
       <c r="B7" t="n">
-        <v>79932</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881195</v>
+        <v>881533</v>
       </c>
       <c r="R7" t="n">
-        <v>7392757</v>
+        <v>7392766</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167929</v>
+        <v>125167913</v>
       </c>
       <c r="B8" t="n">
-        <v>80056</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,34 +1308,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881423</v>
+        <v>881154</v>
       </c>
       <c r="R8" t="n">
-        <v>7392740</v>
+        <v>7392722</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1385,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167916</v>
+        <v>125167939</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>56828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,16 +1414,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1443,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881689</v>
+        <v>881160</v>
       </c>
       <c r="R9" t="n">
-        <v>7392822</v>
+        <v>7392721</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1483,7 +1478,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Avbarkade granar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167927</v>
+        <v>125167940</v>
       </c>
       <c r="B10" t="n">
-        <v>79932</v>
+        <v>56828</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,25 +1517,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881360</v>
+        <v>881680</v>
       </c>
       <c r="R10" t="n">
-        <v>7392796</v>
+        <v>7392834</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1586,6 +1581,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167940</v>
+        <v>125167927</v>
       </c>
       <c r="B11" t="n">
-        <v>56828</v>
+        <v>79932</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,25 +1624,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881680</v>
+        <v>881360</v>
       </c>
       <c r="R11" t="n">
-        <v>7392834</v>
+        <v>7392796</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1688,11 +1688,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125167939</v>
+        <v>125167916</v>
       </c>
       <c r="B12" t="n">
-        <v>56828</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1735,16 +1730,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1759,10 +1754,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>881160</v>
+        <v>881689</v>
       </c>
       <c r="R12" t="n">
-        <v>7392721</v>
+        <v>7392822</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1799,7 +1794,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>Avbarkade granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1826,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167934</v>
+        <v>125167929</v>
       </c>
       <c r="B13" t="n">
-        <v>98269</v>
+        <v>80056</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,25 +1833,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1866,10 +1861,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881252</v>
+        <v>881423</v>
       </c>
       <c r="R13" t="n">
-        <v>7392697</v>
+        <v>7392740</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1928,10 +1923,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167937</v>
+        <v>125167926</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,25 +1935,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1968,10 +1963,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881533</v>
+        <v>881656</v>
       </c>
       <c r="R14" t="n">
-        <v>7392766</v>
+        <v>7392806</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2004,6 +1999,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,10 +2132,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125616388</v>
+        <v>125616394</v>
       </c>
       <c r="B16" t="n">
-        <v>92646</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,25 +2144,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>881292</v>
+        <v>881602</v>
       </c>
       <c r="R16" t="n">
-        <v>7392783</v>
+        <v>7392791</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2234,7 +2234,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125616394</v>
+        <v>125616393</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
@@ -2274,10 +2274,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>881602</v>
+        <v>881422</v>
       </c>
       <c r="R17" t="n">
-        <v>7392791</v>
+        <v>7392746</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125616395</v>
+        <v>125616387</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>79932</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,25 +2348,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2376,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>881585</v>
+        <v>881498</v>
       </c>
       <c r="R18" t="n">
-        <v>7392791</v>
+        <v>7392797</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125616387</v>
+        <v>125616388</v>
       </c>
       <c r="B19" t="n">
-        <v>79932</v>
+        <v>92646</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,25 +2450,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>2079</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>881498</v>
+        <v>881292</v>
       </c>
       <c r="R19" t="n">
-        <v>7392797</v>
+        <v>7392783</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125616393</v>
+        <v>125616395</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>881422</v>
+        <v>881585</v>
       </c>
       <c r="R20" t="n">
-        <v>7392746</v>
+        <v>7392791</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167934</v>
+        <v>125167913</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1100,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881252</v>
+        <v>881154</v>
       </c>
       <c r="R6" t="n">
-        <v>7392697</v>
+        <v>7392722</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1172,6 +1175,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1190,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167937</v>
+        <v>125167939</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>56828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1206,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881533</v>
+        <v>881160</v>
       </c>
       <c r="R7" t="n">
-        <v>7392766</v>
+        <v>7392721</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,6 +1270,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167913</v>
+        <v>125167934</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,41 +1313,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881154</v>
+        <v>881252</v>
       </c>
       <c r="R8" t="n">
-        <v>7392722</v>
+        <v>7392697</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1379,7 +1385,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167939</v>
+        <v>125167937</v>
       </c>
       <c r="B9" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,25 +1415,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881160</v>
+        <v>881533</v>
       </c>
       <c r="R9" t="n">
-        <v>7392721</v>
+        <v>7392766</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1474,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167913</v>
+        <v>125167934</v>
       </c>
       <c r="B6" t="n">
-        <v>91131</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,41 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881154</v>
+        <v>881252</v>
       </c>
       <c r="R6" t="n">
-        <v>7392722</v>
+        <v>7392697</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1175,7 +1172,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1194,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167939</v>
+        <v>125167937</v>
       </c>
       <c r="B7" t="n">
-        <v>56828</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1234,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881160</v>
+        <v>881533</v>
       </c>
       <c r="R7" t="n">
-        <v>7392721</v>
+        <v>7392766</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1270,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167934</v>
+        <v>125167913</v>
       </c>
       <c r="B8" t="n">
-        <v>98269</v>
+        <v>91131</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,38 +1304,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881252</v>
+        <v>881154</v>
       </c>
       <c r="R8" t="n">
-        <v>7392697</v>
+        <v>7392722</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1385,6 +1379,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1403,10 +1398,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167937</v>
+        <v>125167939</v>
       </c>
       <c r="B9" t="n">
-        <v>98269</v>
+        <v>56828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1410,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1438,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881533</v>
+        <v>881160</v>
       </c>
       <c r="R9" t="n">
-        <v>7392766</v>
+        <v>7392721</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1479,6 +1474,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125167935</v>
+        <v>125167929</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>881257</v>
+        <v>881423</v>
       </c>
       <c r="R2" t="n">
-        <v>7392746</v>
+        <v>7392740</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125167938</v>
+        <v>125167937</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>881678</v>
+        <v>881533</v>
       </c>
       <c r="R3" t="n">
-        <v>7392828</v>
+        <v>7392766</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -853,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,12 +872,7 @@
         <v>125167933</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125167928</v>
+        <v>125167913</v>
       </c>
       <c r="B5" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,34 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>881195</v>
+        <v>881154</v>
       </c>
       <c r="R5" t="n">
-        <v>7392757</v>
+        <v>7392722</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1070,6 +1048,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1088,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167934</v>
+        <v>125167928</v>
       </c>
       <c r="B6" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881252</v>
+        <v>881195</v>
       </c>
       <c r="R6" t="n">
-        <v>7392697</v>
+        <v>7392757</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1190,37 +1164,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167937</v>
+        <v>125167926</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881533</v>
+        <v>881656</v>
       </c>
       <c r="R7" t="n">
-        <v>7392766</v>
+        <v>7392806</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1266,6 +1235,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,53 +1266,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125167913</v>
+        <v>125167935</v>
       </c>
       <c r="B8" t="n">
-        <v>91131</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Iso Hiirivaara, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>881154</v>
+        <v>881257</v>
       </c>
       <c r="R8" t="n">
-        <v>7392722</v>
+        <v>7392746</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1379,7 +1345,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1398,37 +1363,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125167939</v>
+        <v>125167927</v>
       </c>
       <c r="B9" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1438,10 +1398,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>881160</v>
+        <v>881360</v>
       </c>
       <c r="R9" t="n">
-        <v>7392721</v>
+        <v>7392796</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1474,11 +1434,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1505,37 +1460,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125167940</v>
+        <v>125167934</v>
       </c>
       <c r="B10" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1495,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>881680</v>
+        <v>881252</v>
       </c>
       <c r="R10" t="n">
-        <v>7392834</v>
+        <v>7392697</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1581,11 +1531,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,37 +1557,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125167927</v>
+        <v>125167940</v>
       </c>
       <c r="B11" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6456</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1592,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>881360</v>
+        <v>881680</v>
       </c>
       <c r="R11" t="n">
-        <v>7392796</v>
+        <v>7392834</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1688,6 +1628,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1717,12 +1662,7 @@
         <v>125167916</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1821,37 +1761,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125167929</v>
+        <v>125167938</v>
       </c>
       <c r="B13" t="n">
-        <v>80056</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1861,10 +1796,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>881423</v>
+        <v>881678</v>
       </c>
       <c r="R13" t="n">
-        <v>7392740</v>
+        <v>7392828</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1897,6 +1832,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 kvm</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,15 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125167926</v>
+        <v>125167939</v>
       </c>
       <c r="B14" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,16 +1874,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1963,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>881656</v>
+        <v>881160</v>
       </c>
       <c r="R14" t="n">
-        <v>7392806</v>
+        <v>7392721</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2003,7 +1938,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Hack på gran</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,15 +1965,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125616392</v>
+        <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2070,10 +2000,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>881164</v>
+        <v>881585</v>
       </c>
       <c r="R15" t="n">
-        <v>7392734</v>
+        <v>7392791</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2132,37 +2062,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125616394</v>
+        <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92700</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2172,10 +2097,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>881602</v>
+        <v>881292</v>
       </c>
       <c r="R16" t="n">
-        <v>7392791</v>
+        <v>7392783</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2234,15 +2159,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125616393</v>
+        <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2274,10 +2194,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>881422</v>
+        <v>881602</v>
       </c>
       <c r="R17" t="n">
-        <v>7392746</v>
+        <v>7392791</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2336,37 +2256,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125616387</v>
+        <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>79932</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2376,10 +2291,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>881498</v>
+        <v>881164</v>
       </c>
       <c r="R18" t="n">
-        <v>7392797</v>
+        <v>7392734</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2438,37 +2353,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125616388</v>
+        <v>125616387</v>
       </c>
       <c r="B19" t="n">
-        <v>92646</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2478,10 +2388,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>881292</v>
+        <v>881498</v>
       </c>
       <c r="R19" t="n">
-        <v>7392783</v>
+        <v>7392797</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2540,15 +2450,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125616395</v>
+        <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2580,10 +2485,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>881585</v>
+        <v>881422</v>
       </c>
       <c r="R20" t="n">
-        <v>7392791</v>
+        <v>7392746</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>125167937</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125167933</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125167913</v>
       </c>
       <c r="B5" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,32 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125167928</v>
+        <v>125167926</v>
       </c>
       <c r="B6" t="n">
-        <v>79974</v>
+        <v>57648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>881195</v>
+        <v>881656</v>
       </c>
       <c r="R6" t="n">
-        <v>7392757</v>
+        <v>7392806</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1138,6 +1138,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1164,32 +1169,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125167926</v>
+        <v>125167928</v>
       </c>
       <c r="B7" t="n">
-        <v>57648</v>
+        <v>79974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1199,10 +1204,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>881656</v>
+        <v>881195</v>
       </c>
       <c r="R7" t="n">
-        <v>7392806</v>
+        <v>7392757</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1235,11 +1240,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,7 +1269,7 @@
         <v>125167935</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>125167934</v>
       </c>
       <c r="B10" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>125167938</v>
       </c>
       <c r="B13" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92700</v>
+        <v>92707</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92707</v>
+        <v>92710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>125616387</v>
       </c>
       <c r="B19" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92710</v>
+        <v>92714</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>125616387</v>
       </c>
       <c r="B19" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
         <v>125616387</v>
       </c>
       <c r="B19" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92716</v>
+        <v>92718</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -1968,7 +1968,7 @@
         <v>125616395</v>
       </c>
       <c r="B15" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>125616388</v>
       </c>
       <c r="B16" t="n">
-        <v>92718</v>
+        <v>92720</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>125616394</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
         <v>125616392</v>
       </c>
       <c r="B18" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>125616393</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2545,6 +2545,5412 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128533267</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>881408</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7392742</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128533245</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>881325</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7392791</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128533260</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>881475</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7392799</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128533265</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>881492</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7392817</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128533269</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>881432</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7392747</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128533271</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>881485</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7392748</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128533256</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>881424</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7392843</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128533253</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>881402</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7392826</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128533199</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>881442</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7392777</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128533206</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>881322</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7392762</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128533216</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>881252</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7392749</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128533218</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>881211</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7392735</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128533204</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>881323</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7392735</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128533203</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>881337</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7392694</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128533277</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>881559</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7392773</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128533274</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>881567</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7392814</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128533198</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>881453</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7392765</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128533261</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>881480</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7392787</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128533243</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>881372</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7392809</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128533273</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>881560</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7392806</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128533251</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>881391</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7392824</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128533201</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>881389</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7392777</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128533288</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>881686</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7392837</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128533257</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>881426</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7392835</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128533285</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>881598</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7392778</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128533263</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>881487</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7392830</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128533282</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>881577</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7392766</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128533275</v>
+      </c>
+      <c r="B48" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>881558</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7392801</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128533270</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>881552</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7392812</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128533280</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>881552</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7392771</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128533240</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>881340</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7392811</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128533207</v>
+      </c>
+      <c r="B52" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>881307</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7392765</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128533242</v>
+      </c>
+      <c r="B53" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>881322</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7392804</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128533241</v>
+      </c>
+      <c r="B54" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>881366</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7392814</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128533217</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>881232</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7392756</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128533254</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>881411</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7392826</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128533258</v>
+      </c>
+      <c r="B57" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>881434</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7392817</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128533266</v>
+      </c>
+      <c r="B58" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>881495</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7392811</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128533281</v>
+      </c>
+      <c r="B59" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>881558</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7392756</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128533239</v>
+      </c>
+      <c r="B60" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>881352</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7392806</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128533200</v>
+      </c>
+      <c r="B61" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>881439</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7392743</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128533283</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>881591</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7392785</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128533247</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>881386</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7392824</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128533259</v>
+      </c>
+      <c r="B64" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>881451</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7392815</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128533286</v>
+      </c>
+      <c r="B65" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>881680</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7392839</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128533264</v>
+      </c>
+      <c r="B66" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>881509</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7392818</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128533255</v>
+      </c>
+      <c r="B67" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>881416</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7392840</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128533289</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>881683</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7392836</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128533276</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>881548</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7392765</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128533202</v>
+      </c>
+      <c r="B70" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>881375</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7392760</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128533279</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Kuivakangas, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>881558</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7392768</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Övertorneå</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -2547,7 +2547,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533267</v>
+        <v>128533260</v>
       </c>
       <c r="B21" t="n">
         <v>98571</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881408</v>
+        <v>881475</v>
       </c>
       <c r="R21" t="n">
-        <v>7392742</v>
+        <v>7392799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128533260</v>
+        <v>128533271</v>
       </c>
       <c r="B23" t="n">
         <v>98571</v>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>881475</v>
+        <v>881485</v>
       </c>
       <c r="R23" t="n">
-        <v>7392799</v>
+        <v>7392748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,7 +2865,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533265</v>
+        <v>128533267</v>
       </c>
       <c r="B24" t="n">
         <v>98571</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>881492</v>
+        <v>881408</v>
       </c>
       <c r="R24" t="n">
-        <v>7392817</v>
+        <v>7392742</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533269</v>
+        <v>128533253</v>
       </c>
       <c r="B25" t="n">
         <v>98571</v>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>881432</v>
+        <v>881402</v>
       </c>
       <c r="R25" t="n">
-        <v>7392747</v>
+        <v>7392826</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128533271</v>
+        <v>128533256</v>
       </c>
       <c r="B26" t="n">
         <v>98571</v>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>881485</v>
+        <v>881424</v>
       </c>
       <c r="R26" t="n">
-        <v>7392748</v>
+        <v>7392843</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533256</v>
+        <v>128533269</v>
       </c>
       <c r="B27" t="n">
         <v>98571</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>881424</v>
+        <v>881432</v>
       </c>
       <c r="R27" t="n">
-        <v>7392843</v>
+        <v>7392747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128533253</v>
+        <v>128533265</v>
       </c>
       <c r="B28" t="n">
         <v>98571</v>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>881402</v>
+        <v>881492</v>
       </c>
       <c r="R28" t="n">
-        <v>7392826</v>
+        <v>7392817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3607,7 +3607,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128533216</v>
+        <v>128533218</v>
       </c>
       <c r="B31" t="n">
         <v>98571</v>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3646,10 +3646,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>881252</v>
+        <v>881211</v>
       </c>
       <c r="R31" t="n">
-        <v>7392749</v>
+        <v>7392735</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128533218</v>
+        <v>128533216</v>
       </c>
       <c r="B32" t="n">
         <v>98571</v>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>881211</v>
+        <v>881252</v>
       </c>
       <c r="R32" t="n">
-        <v>7392735</v>
+        <v>7392749</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128533277</v>
+        <v>128533274</v>
       </c>
       <c r="B35" t="n">
         <v>98571</v>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>881559</v>
+        <v>881567</v>
       </c>
       <c r="R35" t="n">
-        <v>7392773</v>
+        <v>7392814</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128533274</v>
+        <v>128533277</v>
       </c>
       <c r="B36" t="n">
         <v>98571</v>
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>881567</v>
+        <v>881559</v>
       </c>
       <c r="R36" t="n">
-        <v>7392814</v>
+        <v>7392773</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,7 +4243,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128533198</v>
+        <v>128533261</v>
       </c>
       <c r="B37" t="n">
         <v>98571</v>
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>881453</v>
+        <v>881480</v>
       </c>
       <c r="R37" t="n">
-        <v>7392765</v>
+        <v>7392787</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128533261</v>
+        <v>128533243</v>
       </c>
       <c r="B38" t="n">
         <v>98571</v>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>881480</v>
+        <v>881372</v>
       </c>
       <c r="R38" t="n">
-        <v>7392787</v>
+        <v>7392809</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,7 +4455,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128533243</v>
+        <v>128533198</v>
       </c>
       <c r="B39" t="n">
         <v>98571</v>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>881372</v>
+        <v>881453</v>
       </c>
       <c r="R39" t="n">
-        <v>7392809</v>
+        <v>7392765</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128533273</v>
+        <v>128533288</v>
       </c>
       <c r="B40" t="n">
         <v>98571</v>
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>881560</v>
+        <v>881686</v>
       </c>
       <c r="R40" t="n">
-        <v>7392806</v>
+        <v>7392837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,7 +4667,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128533251</v>
+        <v>128533285</v>
       </c>
       <c r="B41" t="n">
         <v>98571</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>881391</v>
+        <v>881598</v>
       </c>
       <c r="R41" t="n">
-        <v>7392824</v>
+        <v>7392778</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,7 +4773,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128533201</v>
+        <v>128533251</v>
       </c>
       <c r="B42" t="n">
         <v>98571</v>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>881389</v>
+        <v>881391</v>
       </c>
       <c r="R42" t="n">
-        <v>7392777</v>
+        <v>7392824</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128533288</v>
+        <v>128533257</v>
       </c>
       <c r="B43" t="n">
         <v>98571</v>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>881686</v>
+        <v>881426</v>
       </c>
       <c r="R43" t="n">
-        <v>7392837</v>
+        <v>7392835</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,7 +4985,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128533257</v>
+        <v>128533273</v>
       </c>
       <c r="B44" t="n">
         <v>98571</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>881426</v>
+        <v>881560</v>
       </c>
       <c r="R44" t="n">
-        <v>7392835</v>
+        <v>7392806</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128533285</v>
+        <v>128533263</v>
       </c>
       <c r="B45" t="n">
         <v>98571</v>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>881598</v>
+        <v>881487</v>
       </c>
       <c r="R45" t="n">
-        <v>7392778</v>
+        <v>7392830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,7 +5197,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128533263</v>
+        <v>128533201</v>
       </c>
       <c r="B46" t="n">
         <v>98571</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>881487</v>
+        <v>881389</v>
       </c>
       <c r="R46" t="n">
-        <v>7392830</v>
+        <v>7392777</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128533241</v>
+        <v>128533254</v>
       </c>
       <c r="B54" t="n">
         <v>98571</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>881366</v>
+        <v>881411</v>
       </c>
       <c r="R54" t="n">
-        <v>7392814</v>
+        <v>7392826</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128533217</v>
+        <v>128533241</v>
       </c>
       <c r="B55" t="n">
         <v>98571</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>881232</v>
+        <v>881366</v>
       </c>
       <c r="R55" t="n">
-        <v>7392756</v>
+        <v>7392814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128533254</v>
+        <v>128533217</v>
       </c>
       <c r="B56" t="n">
         <v>98571</v>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>881411</v>
+        <v>881232</v>
       </c>
       <c r="R56" t="n">
-        <v>7392826</v>
+        <v>7392756</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128533266</v>
+        <v>128533281</v>
       </c>
       <c r="B58" t="n">
         <v>98571</v>
@@ -6499,7 +6499,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6508,10 +6508,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>881495</v>
+        <v>881558</v>
       </c>
       <c r="R58" t="n">
-        <v>7392811</v>
+        <v>7392756</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6575,7 +6575,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128533281</v>
+        <v>128533266</v>
       </c>
       <c r="B59" t="n">
         <v>98571</v>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>881558</v>
+        <v>881495</v>
       </c>
       <c r="R59" t="n">
-        <v>7392756</v>
+        <v>7392811</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128533239</v>
+        <v>128533200</v>
       </c>
       <c r="B60" t="n">
         <v>98571</v>
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6720,10 +6720,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>881352</v>
+        <v>881439</v>
       </c>
       <c r="R60" t="n">
-        <v>7392806</v>
+        <v>7392743</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6787,7 +6787,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128533200</v>
+        <v>128533283</v>
       </c>
       <c r="B61" t="n">
         <v>98571</v>
@@ -6826,10 +6826,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>881439</v>
+        <v>881591</v>
       </c>
       <c r="R61" t="n">
-        <v>7392743</v>
+        <v>7392785</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6893,7 +6893,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128533283</v>
+        <v>128533247</v>
       </c>
       <c r="B62" t="n">
         <v>98571</v>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6932,10 +6932,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>881591</v>
+        <v>881386</v>
       </c>
       <c r="R62" t="n">
-        <v>7392785</v>
+        <v>7392824</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6999,7 +6999,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128533247</v>
+        <v>128533239</v>
       </c>
       <c r="B63" t="n">
         <v>98571</v>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7038,10 +7038,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>881386</v>
+        <v>881352</v>
       </c>
       <c r="R63" t="n">
-        <v>7392824</v>
+        <v>7392806</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128533264</v>
+        <v>128533289</v>
       </c>
       <c r="B66" t="n">
         <v>98571</v>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>881509</v>
+        <v>881683</v>
       </c>
       <c r="R66" t="n">
-        <v>7392818</v>
+        <v>7392836</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7529,7 +7529,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128533289</v>
+        <v>128533264</v>
       </c>
       <c r="B68" t="n">
         <v>98571</v>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7568,10 +7568,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>881683</v>
+        <v>881509</v>
       </c>
       <c r="R68" t="n">
-        <v>7392836</v>
+        <v>7392818</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7741,7 +7741,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128533202</v>
+        <v>128533279</v>
       </c>
       <c r="B70" t="n">
         <v>98571</v>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7780,10 +7780,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>881375</v>
+        <v>881558</v>
       </c>
       <c r="R70" t="n">
-        <v>7392760</v>
+        <v>7392768</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7847,7 +7847,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128533279</v>
+        <v>128533202</v>
       </c>
       <c r="B71" t="n">
         <v>98571</v>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -7886,10 +7886,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>881558</v>
+        <v>881375</v>
       </c>
       <c r="R71" t="n">
-        <v>7392768</v>
+        <v>7392760</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -5303,7 +5303,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128533282</v>
+        <v>128533275</v>
       </c>
       <c r="B47" t="n">
         <v>98571</v>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>881577</v>
+        <v>881558</v>
       </c>
       <c r="R47" t="n">
-        <v>7392766</v>
+        <v>7392801</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128533275</v>
+        <v>128533282</v>
       </c>
       <c r="B48" t="n">
         <v>98571</v>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>881558</v>
+        <v>881577</v>
       </c>
       <c r="R48" t="n">
-        <v>7392801</v>
+        <v>7392766</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128533254</v>
+        <v>128533258</v>
       </c>
       <c r="B54" t="n">
         <v>98571</v>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>881411</v>
+        <v>881434</v>
       </c>
       <c r="R54" t="n">
-        <v>7392826</v>
+        <v>7392817</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128533241</v>
+        <v>128533254</v>
       </c>
       <c r="B55" t="n">
         <v>98571</v>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6190,10 +6190,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>881366</v>
+        <v>881411</v>
       </c>
       <c r="R55" t="n">
-        <v>7392814</v>
+        <v>7392826</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6257,7 +6257,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128533217</v>
+        <v>128533241</v>
       </c>
       <c r="B56" t="n">
         <v>98571</v>
@@ -6287,7 +6287,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6296,10 +6296,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>881232</v>
+        <v>881366</v>
       </c>
       <c r="R56" t="n">
-        <v>7392756</v>
+        <v>7392814</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6363,7 +6363,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128533258</v>
+        <v>128533217</v>
       </c>
       <c r="B57" t="n">
         <v>98571</v>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>881434</v>
+        <v>881232</v>
       </c>
       <c r="R57" t="n">
-        <v>7392817</v>
+        <v>7392756</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -2547,10 +2547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533260</v>
+        <v>128533245</v>
       </c>
       <c r="B21" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881475</v>
+        <v>881325</v>
       </c>
       <c r="R21" t="n">
-        <v>7392799</v>
+        <v>7392791</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533245</v>
+        <v>128533271</v>
       </c>
       <c r="B22" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881325</v>
+        <v>881485</v>
       </c>
       <c r="R22" t="n">
-        <v>7392791</v>
+        <v>7392748</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128533271</v>
+        <v>128533260</v>
       </c>
       <c r="B23" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>881485</v>
+        <v>881475</v>
       </c>
       <c r="R23" t="n">
-        <v>7392748</v>
+        <v>7392799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2868,7 +2868,7 @@
         <v>128533267</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>128533253</v>
       </c>
       <c r="B25" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>128533256</v>
       </c>
       <c r="B26" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>128533269</v>
       </c>
       <c r="B27" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128533265</v>
       </c>
       <c r="B28" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>128533199</v>
       </c>
       <c r="B29" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>128533206</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128533218</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>128533216</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128533204</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128533203</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128533274</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>128533277</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>128533261</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128533243</v>
+        <v>128533198</v>
       </c>
       <c r="B38" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4388,10 +4388,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>881372</v>
+        <v>881453</v>
       </c>
       <c r="R38" t="n">
-        <v>7392809</v>
+        <v>7392765</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128533198</v>
+        <v>128533243</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>881453</v>
+        <v>881372</v>
       </c>
       <c r="R39" t="n">
-        <v>7392765</v>
+        <v>7392809</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128533288</v>
+        <v>128533285</v>
       </c>
       <c r="B40" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>881686</v>
+        <v>881598</v>
       </c>
       <c r="R40" t="n">
-        <v>7392837</v>
+        <v>7392778</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128533285</v>
+        <v>128533251</v>
       </c>
       <c r="B41" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>881598</v>
+        <v>881391</v>
       </c>
       <c r="R41" t="n">
-        <v>7392778</v>
+        <v>7392824</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128533251</v>
+        <v>128533288</v>
       </c>
       <c r="B42" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>881391</v>
+        <v>881686</v>
       </c>
       <c r="R42" t="n">
-        <v>7392824</v>
+        <v>7392837</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4882,7 +4882,7 @@
         <v>128533257</v>
       </c>
       <c r="B43" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>128533273</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>128533263</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>128533201</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5303,10 +5303,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128533275</v>
+        <v>128533282</v>
       </c>
       <c r="B47" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5342,10 +5342,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>881558</v>
+        <v>881577</v>
       </c>
       <c r="R47" t="n">
-        <v>7392801</v>
+        <v>7392766</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5409,10 +5409,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128533282</v>
+        <v>128533275</v>
       </c>
       <c r="B48" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5448,10 +5448,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>881577</v>
+        <v>881558</v>
       </c>
       <c r="R48" t="n">
-        <v>7392766</v>
+        <v>7392801</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5518,7 +5518,7 @@
         <v>128533270</v>
       </c>
       <c r="B49" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>128533280</v>
       </c>
       <c r="B50" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>128533240</v>
       </c>
       <c r="B51" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128533207</v>
       </c>
       <c r="B52" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128533242</v>
       </c>
       <c r="B53" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>128533258</v>
       </c>
       <c r="B54" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>128533254</v>
       </c>
       <c r="B55" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>128533241</v>
       </c>
       <c r="B56" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>128533217</v>
       </c>
       <c r="B57" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>128533281</v>
       </c>
       <c r="B58" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128533266</v>
       </c>
       <c r="B59" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>128533200</v>
       </c>
       <c r="B60" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>128533283</v>
       </c>
       <c r="B61" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>128533247</v>
       </c>
       <c r="B62" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>128533239</v>
       </c>
       <c r="B63" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>128533259</v>
       </c>
       <c r="B64" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128533286</v>
       </c>
       <c r="B65" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>128533289</v>
       </c>
       <c r="B66" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128533255</v>
       </c>
       <c r="B67" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>128533264</v>
       </c>
       <c r="B68" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>128533276</v>
       </c>
       <c r="B69" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128533279</v>
       </c>
       <c r="B70" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128533202</v>
       </c>
       <c r="B71" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -2550,7 +2550,7 @@
         <v>128533245</v>
       </c>
       <c r="B21" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128533271</v>
       </c>
       <c r="B22" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128533260</v>
       </c>
       <c r="B23" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>128533267</v>
       </c>
       <c r="B24" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>128533253</v>
       </c>
       <c r="B25" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>128533256</v>
       </c>
       <c r="B26" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>128533269</v>
       </c>
       <c r="B27" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128533265</v>
       </c>
       <c r="B28" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>128533199</v>
       </c>
       <c r="B29" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>128533206</v>
       </c>
       <c r="B30" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128533218</v>
       </c>
       <c r="B31" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>128533216</v>
       </c>
       <c r="B32" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128533204</v>
       </c>
       <c r="B33" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128533203</v>
       </c>
       <c r="B34" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128533274</v>
       </c>
       <c r="B35" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>128533277</v>
       </c>
       <c r="B36" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>128533261</v>
       </c>
       <c r="B37" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>128533198</v>
       </c>
       <c r="B38" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128533243</v>
       </c>
       <c r="B39" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128533285</v>
       </c>
       <c r="B40" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>128533251</v>
       </c>
       <c r="B41" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128533288</v>
       </c>
       <c r="B42" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>128533257</v>
       </c>
       <c r="B43" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>128533273</v>
       </c>
       <c r="B44" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>128533263</v>
       </c>
       <c r="B45" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>128533201</v>
       </c>
       <c r="B46" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>128533282</v>
       </c>
       <c r="B47" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128533275</v>
       </c>
       <c r="B48" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128533270</v>
       </c>
       <c r="B49" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>128533280</v>
       </c>
       <c r="B50" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>128533240</v>
       </c>
       <c r="B51" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128533207</v>
       </c>
       <c r="B52" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128533242</v>
       </c>
       <c r="B53" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>128533258</v>
       </c>
       <c r="B54" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>128533254</v>
       </c>
       <c r="B55" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>128533241</v>
       </c>
       <c r="B56" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>128533217</v>
       </c>
       <c r="B57" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>128533281</v>
       </c>
       <c r="B58" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128533266</v>
       </c>
       <c r="B59" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>128533200</v>
       </c>
       <c r="B60" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>128533283</v>
       </c>
       <c r="B61" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>128533247</v>
       </c>
       <c r="B62" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>128533239</v>
       </c>
       <c r="B63" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>128533259</v>
       </c>
       <c r="B64" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128533286</v>
       </c>
       <c r="B65" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>128533289</v>
       </c>
       <c r="B66" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128533255</v>
       </c>
       <c r="B67" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>128533264</v>
       </c>
       <c r="B68" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>128533276</v>
       </c>
       <c r="B69" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128533279</v>
       </c>
       <c r="B70" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128533202</v>
       </c>
       <c r="B71" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -2550,7 +2550,7 @@
         <v>128533245</v>
       </c>
       <c r="B21" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>128533271</v>
       </c>
       <c r="B22" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>128533260</v>
       </c>
       <c r="B23" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>128533267</v>
       </c>
       <c r="B24" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>128533253</v>
       </c>
       <c r="B25" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>128533256</v>
       </c>
       <c r="B26" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3186,7 +3186,7 @@
         <v>128533269</v>
       </c>
       <c r="B27" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>128533265</v>
       </c>
       <c r="B28" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>128533199</v>
       </c>
       <c r="B29" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>128533206</v>
       </c>
       <c r="B30" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128533218</v>
       </c>
       <c r="B31" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>128533216</v>
       </c>
       <c r="B32" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128533204</v>
       </c>
       <c r="B33" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128533203</v>
       </c>
       <c r="B34" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128533274</v>
       </c>
       <c r="B35" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>128533277</v>
       </c>
       <c r="B36" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>128533261</v>
       </c>
       <c r="B37" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>128533198</v>
       </c>
       <c r="B38" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128533243</v>
       </c>
       <c r="B39" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4564,7 +4564,7 @@
         <v>128533285</v>
       </c>
       <c r="B40" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>128533251</v>
       </c>
       <c r="B41" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>128533288</v>
       </c>
       <c r="B42" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>128533257</v>
       </c>
       <c r="B43" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>128533273</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5094,7 +5094,7 @@
         <v>128533263</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>128533201</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         <v>128533282</v>
       </c>
       <c r="B47" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128533275</v>
       </c>
       <c r="B48" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>128533270</v>
       </c>
       <c r="B49" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>128533280</v>
       </c>
       <c r="B50" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>128533240</v>
       </c>
       <c r="B51" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128533207</v>
       </c>
       <c r="B52" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128533242</v>
       </c>
       <c r="B53" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>128533258</v>
       </c>
       <c r="B54" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>128533254</v>
       </c>
       <c r="B55" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>128533241</v>
       </c>
       <c r="B56" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>128533217</v>
       </c>
       <c r="B57" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>128533281</v>
       </c>
       <c r="B58" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128533266</v>
       </c>
       <c r="B59" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>128533200</v>
       </c>
       <c r="B60" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>128533283</v>
       </c>
       <c r="B61" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>128533247</v>
       </c>
       <c r="B62" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>128533239</v>
       </c>
       <c r="B63" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>128533259</v>
       </c>
       <c r="B64" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128533286</v>
       </c>
       <c r="B65" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>128533289</v>
       </c>
       <c r="B66" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128533255</v>
       </c>
       <c r="B67" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>128533264</v>
       </c>
       <c r="B68" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>128533276</v>
       </c>
       <c r="B69" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128533279</v>
       </c>
       <c r="B70" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128533202</v>
       </c>
       <c r="B71" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -2547,10 +2547,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128533245</v>
+        <v>128533260</v>
       </c>
       <c r="B21" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2586,10 +2586,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>881325</v>
+        <v>881475</v>
       </c>
       <c r="R21" t="n">
-        <v>7392791</v>
+        <v>7392799</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128533271</v>
+        <v>128533267</v>
       </c>
       <c r="B22" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>881485</v>
+        <v>881408</v>
       </c>
       <c r="R22" t="n">
-        <v>7392748</v>
+        <v>7392742</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2759,10 +2759,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128533260</v>
+        <v>128533256</v>
       </c>
       <c r="B23" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,10 +2798,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>881475</v>
+        <v>881424</v>
       </c>
       <c r="R23" t="n">
-        <v>7392799</v>
+        <v>7392843</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2865,10 +2865,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128533267</v>
+        <v>128533269</v>
       </c>
       <c r="B24" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>881408</v>
+        <v>881432</v>
       </c>
       <c r="R24" t="n">
-        <v>7392742</v>
+        <v>7392747</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2971,10 +2971,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128533253</v>
+        <v>128533245</v>
       </c>
       <c r="B25" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3010,10 +3010,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>881402</v>
+        <v>881325</v>
       </c>
       <c r="R25" t="n">
-        <v>7392826</v>
+        <v>7392791</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3077,10 +3077,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128533256</v>
+        <v>128533271</v>
       </c>
       <c r="B26" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3116,10 +3116,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>881424</v>
+        <v>881485</v>
       </c>
       <c r="R26" t="n">
-        <v>7392843</v>
+        <v>7392748</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128533269</v>
+        <v>128533253</v>
       </c>
       <c r="B27" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>881432</v>
+        <v>881402</v>
       </c>
       <c r="R27" t="n">
-        <v>7392747</v>
+        <v>7392826</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3292,7 +3292,7 @@
         <v>128533265</v>
       </c>
       <c r="B28" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3398,7 +3398,7 @@
         <v>128533199</v>
       </c>
       <c r="B29" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3504,7 +3504,7 @@
         <v>128533206</v>
       </c>
       <c r="B30" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         <v>128533218</v>
       </c>
       <c r="B31" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>128533216</v>
       </c>
       <c r="B32" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>128533204</v>
       </c>
       <c r="B33" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>128533203</v>
       </c>
       <c r="B34" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>128533274</v>
       </c>
       <c r="B35" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
         <v>128533277</v>
       </c>
       <c r="B36" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>128533261</v>
       </c>
       <c r="B37" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>128533198</v>
       </c>
       <c r="B38" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
         <v>128533243</v>
       </c>
       <c r="B39" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4561,10 +4561,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128533285</v>
+        <v>128533251</v>
       </c>
       <c r="B40" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4600,10 +4600,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>881598</v>
+        <v>881391</v>
       </c>
       <c r="R40" t="n">
-        <v>7392778</v>
+        <v>7392824</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128533251</v>
+        <v>128533288</v>
       </c>
       <c r="B41" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>881391</v>
+        <v>881686</v>
       </c>
       <c r="R41" t="n">
-        <v>7392824</v>
+        <v>7392837</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4773,10 +4773,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128533288</v>
+        <v>128533257</v>
       </c>
       <c r="B42" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4812,10 +4812,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>881686</v>
+        <v>881426</v>
       </c>
       <c r="R42" t="n">
-        <v>7392837</v>
+        <v>7392835</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4879,10 +4879,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128533257</v>
+        <v>128533273</v>
       </c>
       <c r="B43" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>881426</v>
+        <v>881560</v>
       </c>
       <c r="R43" t="n">
-        <v>7392835</v>
+        <v>7392806</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4985,10 +4985,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128533273</v>
+        <v>128533263</v>
       </c>
       <c r="B44" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5024,10 +5024,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>881560</v>
+        <v>881487</v>
       </c>
       <c r="R44" t="n">
-        <v>7392806</v>
+        <v>7392830</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5091,10 +5091,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128533263</v>
+        <v>128533201</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5130,10 +5130,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>881487</v>
+        <v>881389</v>
       </c>
       <c r="R45" t="n">
-        <v>7392830</v>
+        <v>7392777</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5197,10 +5197,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128533201</v>
+        <v>128533285</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5236,10 +5236,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>881389</v>
+        <v>881598</v>
       </c>
       <c r="R46" t="n">
-        <v>7392777</v>
+        <v>7392778</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5306,7 +5306,7 @@
         <v>128533282</v>
       </c>
       <c r="B47" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>128533275</v>
       </c>
       <c r="B48" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5515,10 +5515,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128533270</v>
+        <v>128533280</v>
       </c>
       <c r="B49" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5557,7 +5557,7 @@
         <v>881552</v>
       </c>
       <c r="R49" t="n">
-        <v>7392812</v>
+        <v>7392771</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,10 +5621,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128533280</v>
+        <v>128533270</v>
       </c>
       <c r="B50" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5663,7 +5663,7 @@
         <v>881552</v>
       </c>
       <c r="R50" t="n">
-        <v>7392771</v>
+        <v>7392812</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5730,7 +5730,7 @@
         <v>128533240</v>
       </c>
       <c r="B51" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         <v>128533207</v>
       </c>
       <c r="B52" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>128533242</v>
       </c>
       <c r="B53" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>128533258</v>
       </c>
       <c r="B54" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>128533254</v>
       </c>
       <c r="B55" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
         <v>128533241</v>
       </c>
       <c r="B56" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         <v>128533217</v>
       </c>
       <c r="B57" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>128533281</v>
       </c>
       <c r="B58" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         <v>128533266</v>
       </c>
       <c r="B59" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>128533200</v>
       </c>
       <c r="B60" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>128533283</v>
       </c>
       <c r="B61" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>128533247</v>
       </c>
       <c r="B62" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>128533239</v>
       </c>
       <c r="B63" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>128533259</v>
       </c>
       <c r="B64" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>128533286</v>
       </c>
       <c r="B65" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7320,7 +7320,7 @@
         <v>128533289</v>
       </c>
       <c r="B66" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>128533255</v>
       </c>
       <c r="B67" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         <v>128533264</v>
       </c>
       <c r="B68" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>128533276</v>
       </c>
       <c r="B69" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>128533279</v>
       </c>
       <c r="B70" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>128533202</v>
       </c>
       <c r="B71" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>

--- a/artfynd/A 15495-2022 artfynd.xlsx
+++ b/artfynd/A 15495-2022 artfynd.xlsx
@@ -5515,7 +5515,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128533280</v>
+        <v>128533270</v>
       </c>
       <c r="B49" t="n">
         <v>98591</v>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5557,7 +5557,7 @@
         <v>881552</v>
       </c>
       <c r="R49" t="n">
-        <v>7392771</v>
+        <v>7392812</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128533270</v>
+        <v>128533280</v>
       </c>
       <c r="B50" t="n">
         <v>98591</v>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5663,7 +5663,7 @@
         <v>881552</v>
       </c>
       <c r="R50" t="n">
-        <v>7392812</v>
+        <v>7392771</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
